--- a/likert_items.xlsx
+++ b/likert_items.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micky\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPPA\CMKL\Animation_Project\Summer\Experiment_Workflows\Testing1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B91187-0753-48A1-AE8D-AA12785766C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E01245-21B7-4560-8F17-E0B5198CEA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="17472" windowHeight="10992" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,30 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>itemText</t>
   </si>
   <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>options</t>
-  </si>
-  <si>
-    <t>layout</t>
-  </si>
-  <si>
     <t>The video held my attention throughout.</t>
-  </si>
-  <si>
-    <t>rating</t>
-  </si>
-  <si>
-    <t>1,2,3,4,5</t>
-  </si>
-  <si>
-    <t>horiz</t>
   </si>
   <si>
     <t>The speaker was easy to understand.</t>
@@ -320,92 +302,56 @@
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="12.609375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="33" customWidth="1"/>
+    <col min="1" max="1" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>7</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>7</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>7</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/likert_items.xlsx
+++ b/likert_items.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPPA\CMKL\Animation_Project\Summer\Experiment_Workflows\Testing1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E01245-21B7-4560-8F17-E0B5198CEA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71138C64-3A40-4008-ABDE-2D212CE58604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="17472" windowHeight="10992" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,13 +31,13 @@
     <t>The speaker was easy to understand.</t>
   </si>
   <si>
-    <t>I found the content engaging.</t>
-  </si>
-  <si>
     <t>I would want to watch more videos like this.</t>
   </si>
   <si>
-    <t>The pacing of the video felt appropriate.</t>
+    <t>The content was interesting.</t>
+  </si>
+  <si>
+    <t>The speed of the video felt appropriate.</t>
   </si>
 </sst>
 </file>
@@ -331,7 +331,7 @@
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -339,7 +339,7 @@
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
